--- a/artfynd/A 21987-2025 artfynd.xlsx
+++ b/artfynd/A 21987-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126051180</v>
       </c>
       <c r="B2" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126051265</v>
       </c>
       <c r="B3" t="n">
-        <v>91682</v>
+        <v>91686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126051072</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126051394</v>
+        <v>126051096</v>
       </c>
       <c r="B5" t="n">
-        <v>57755</v>
+        <v>80103</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,43 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599720</v>
+        <v>599740</v>
       </c>
       <c r="R5" t="n">
-        <v>7054210</v>
+        <v>7054236</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1072,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126051096</v>
+        <v>126051394</v>
       </c>
       <c r="B6" t="n">
-        <v>80099</v>
+        <v>57755</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,34 +1074,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599740</v>
+        <v>599720</v>
       </c>
       <c r="R6" t="n">
-        <v>7054236</v>
+        <v>7054210</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1172,7 +1172,7 @@
         <v>126051445</v>
       </c>
       <c r="B7" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>126051454</v>
       </c>
       <c r="B8" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 21987-2025 artfynd.xlsx
+++ b/artfynd/A 21987-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126051180</v>
       </c>
       <c r="B2" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126051265</v>
       </c>
       <c r="B3" t="n">
-        <v>91686</v>
+        <v>91688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126051072</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126051096</v>
       </c>
       <c r="B5" t="n">
-        <v>80103</v>
+        <v>80104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126051394</v>
       </c>
       <c r="B6" t="n">
-        <v>57755</v>
+        <v>57756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>126051445</v>
       </c>
       <c r="B7" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>126051454</v>
       </c>
       <c r="B8" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 21987-2025 artfynd.xlsx
+++ b/artfynd/A 21987-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126051180</v>
       </c>
       <c r="B2" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126051265</v>
       </c>
       <c r="B3" t="n">
-        <v>91688</v>
+        <v>91690</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126051096</v>
+        <v>126051394</v>
       </c>
       <c r="B5" t="n">
-        <v>80104</v>
+        <v>57756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599740</v>
+        <v>599720</v>
       </c>
       <c r="R5" t="n">
-        <v>7054236</v>
+        <v>7054210</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126051394</v>
+        <v>126051096</v>
       </c>
       <c r="B6" t="n">
-        <v>57756</v>
+        <v>80104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,43 +1083,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599720</v>
+        <v>599740</v>
       </c>
       <c r="R6" t="n">
-        <v>7054210</v>
+        <v>7054236</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 21987-2025 artfynd.xlsx
+++ b/artfynd/A 21987-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126051180</v>
       </c>
       <c r="B2" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126051265</v>
       </c>
       <c r="B3" t="n">
-        <v>91690</v>
+        <v>91692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126051394</v>
+        <v>126051096</v>
       </c>
       <c r="B5" t="n">
-        <v>57756</v>
+        <v>80104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,43 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599720</v>
+        <v>599740</v>
       </c>
       <c r="R5" t="n">
-        <v>7054210</v>
+        <v>7054236</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1072,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126051096</v>
+        <v>126051394</v>
       </c>
       <c r="B6" t="n">
-        <v>80104</v>
+        <v>57756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,34 +1074,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599740</v>
+        <v>599720</v>
       </c>
       <c r="R6" t="n">
-        <v>7054236</v>
+        <v>7054210</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 21987-2025 artfynd.xlsx
+++ b/artfynd/A 21987-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126051180</v>
       </c>
       <c r="B2" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126051265</v>
       </c>
       <c r="B3" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126051072</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126051096</v>
       </c>
       <c r="B5" t="n">
-        <v>80104</v>
+        <v>80108</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126051394</v>
       </c>
       <c r="B6" t="n">
-        <v>57756</v>
+        <v>57760</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>126051445</v>
       </c>
       <c r="B7" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>126051454</v>
       </c>
       <c r="B8" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 21987-2025 artfynd.xlsx
+++ b/artfynd/A 21987-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126051180</v>
       </c>
       <c r="B2" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126051265</v>
       </c>
       <c r="B3" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126051072</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126051096</v>
+        <v>126051394</v>
       </c>
       <c r="B5" t="n">
-        <v>80108</v>
+        <v>57761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599740</v>
+        <v>599720</v>
       </c>
       <c r="R5" t="n">
-        <v>7054236</v>
+        <v>7054210</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126051394</v>
+        <v>126051096</v>
       </c>
       <c r="B6" t="n">
-        <v>57760</v>
+        <v>80111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,43 +1083,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599720</v>
+        <v>599740</v>
       </c>
       <c r="R6" t="n">
-        <v>7054210</v>
+        <v>7054236</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1172,7 +1172,7 @@
         <v>126051445</v>
       </c>
       <c r="B7" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>126051454</v>
       </c>
       <c r="B8" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 21987-2025 artfynd.xlsx
+++ b/artfynd/A 21987-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126051394</v>
+        <v>126051096</v>
       </c>
       <c r="B5" t="n">
-        <v>57761</v>
+        <v>80111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,43 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599720</v>
+        <v>599740</v>
       </c>
       <c r="R5" t="n">
-        <v>7054210</v>
+        <v>7054236</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1072,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126051096</v>
+        <v>126051394</v>
       </c>
       <c r="B6" t="n">
-        <v>80111</v>
+        <v>57761</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,34 +1074,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599740</v>
+        <v>599720</v>
       </c>
       <c r="R6" t="n">
-        <v>7054236</v>
+        <v>7054210</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 21987-2025 artfynd.xlsx
+++ b/artfynd/A 21987-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126051096</v>
+        <v>126051394</v>
       </c>
       <c r="B5" t="n">
-        <v>80111</v>
+        <v>57761</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>599740</v>
+        <v>599720</v>
       </c>
       <c r="R5" t="n">
-        <v>7054236</v>
+        <v>7054210</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1063,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126051394</v>
+        <v>126051096</v>
       </c>
       <c r="B6" t="n">
-        <v>57761</v>
+        <v>80111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,43 +1083,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lövsjöbäcken, Lövsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>599720</v>
+        <v>599740</v>
       </c>
       <c r="R6" t="n">
-        <v>7054210</v>
+        <v>7054236</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
